--- a/results/Summary env variables x community.xlsx
+++ b/results/Summary env variables x community.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>n</t>
   </si>
@@ -68,9 +68,6 @@
     <t>bio1</t>
   </si>
   <si>
-    <t>7   1.81</t>
-  </si>
-  <si>
     <t>bio2</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
   </si>
   <si>
     <t>GDD</t>
-  </si>
-  <si>
-    <t>391.   5</t>
   </si>
   <si>
     <t>Variable</t>
@@ -285,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -293,35 +287,27 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -602,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
@@ -616,12 +602,13 @@
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -659,58 +646,62 @@
       <c r="N1" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="S1" s="21"/>
+      <c r="U1"/>
+    </row>
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="9">
-        <v>51</v>
-      </c>
-      <c r="D2" s="8">
-        <v>2088</v>
-      </c>
-      <c r="E2" s="8">
+      <c r="C2" s="8">
+        <v>48</v>
+      </c>
+      <c r="D2" s="7">
+        <v>2091</v>
+      </c>
+      <c r="E2" s="7">
         <v>2157</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <v>2120</v>
       </c>
-      <c r="G2" s="9">
-        <v>2115</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="G2" s="8">
+        <v>2116</v>
+      </c>
+      <c r="H2" s="8">
         <v>2103</v>
       </c>
-      <c r="I2" s="9">
-        <v>2144</v>
-      </c>
-      <c r="J2" s="9">
-        <v>40.9</v>
-      </c>
-      <c r="K2" s="9">
-        <v>22.3</v>
-      </c>
-      <c r="L2" s="9">
-        <v>21.5</v>
-      </c>
-      <c r="M2" s="9">
-        <v>3.01</v>
-      </c>
-      <c r="N2" s="11">
-        <v>6.04</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
+      <c r="I2" s="16">
+        <v>2145</v>
+      </c>
+      <c r="J2" s="8">
+        <v>41.6</v>
+      </c>
+      <c r="K2" s="8">
+        <v>21.9</v>
+      </c>
+      <c r="L2" s="8">
+        <v>21.4</v>
+      </c>
+      <c r="M2" s="8">
+        <v>3.09</v>
+      </c>
+      <c r="N2" s="10">
+        <v>6.22</v>
+      </c>
+      <c r="S2" s="21"/>
+      <c r="U2"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="19"/>
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1">
         <v>3.37</v>
@@ -719,40 +710,42 @@
         <v>8.5399999999999991</v>
       </c>
       <c r="F3" s="4">
-        <v>6.29</v>
+        <v>6.22</v>
       </c>
       <c r="G3" s="1">
-        <v>6.51</v>
+        <v>6.48</v>
       </c>
       <c r="H3" s="1">
-        <v>5.46</v>
-      </c>
-      <c r="I3" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>14</v>
+        <v>5.42</v>
+      </c>
+      <c r="I3" s="5">
+        <v>7.12</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.7</v>
       </c>
       <c r="K3" s="1">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="L3" s="1">
         <v>1.32</v>
       </c>
       <c r="M3" s="1">
-        <v>0.185</v>
-      </c>
-      <c r="N3" s="13">
-        <v>0.372</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+        <v>0.191</v>
+      </c>
+      <c r="N3" s="11">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="S3" s="21"/>
+      <c r="U3"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="19"/>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1">
         <v>1.99</v>
@@ -761,40 +754,42 @@
         <v>10.8</v>
       </c>
       <c r="F4" s="4">
-        <v>5.47</v>
+        <v>5.42</v>
       </c>
       <c r="G4" s="1">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="H4" s="1">
-        <v>3.92</v>
-      </c>
-      <c r="I4" s="1">
-        <v>6.6</v>
+        <v>3.81</v>
+      </c>
+      <c r="I4" s="5">
+        <v>6.56</v>
       </c>
       <c r="J4" s="1">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="K4" s="1">
-        <v>2.0299999999999998</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="L4" s="1">
         <v>2.15</v>
       </c>
       <c r="M4" s="1">
-        <v>0.30099999999999999</v>
-      </c>
-      <c r="N4" s="13">
-        <v>0.60499999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
+        <v>0.311</v>
+      </c>
+      <c r="N4" s="11">
+        <v>0.625</v>
+      </c>
+      <c r="S4" s="21"/>
+      <c r="U4"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1">
         <v>16.899999999999999</v>
@@ -806,37 +801,39 @@
         <v>26.2</v>
       </c>
       <c r="G5" s="1">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="H5" s="1">
         <v>22.7</v>
       </c>
-      <c r="I5" s="1">
-        <v>29.2</v>
+      <c r="I5" s="5">
+        <v>29.1</v>
       </c>
       <c r="J5" s="1">
-        <v>6.46</v>
+        <v>6.32</v>
       </c>
       <c r="K5" s="1">
-        <v>5.08</v>
+        <v>5.2</v>
       </c>
       <c r="L5" s="1">
-        <v>4.95</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="M5" s="1">
-        <v>0.69299999999999995</v>
-      </c>
-      <c r="N5" s="13">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="N5" s="11">
+        <v>1.44</v>
+      </c>
+      <c r="S5" s="21"/>
+      <c r="U5"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -845,40 +842,42 @@
         <v>145</v>
       </c>
       <c r="F6" s="3">
-        <v>31.8</v>
+        <v>32.5</v>
       </c>
       <c r="G6" s="1">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="H6" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="I6" s="1">
-        <v>43.5</v>
+        <v>8.75</v>
+      </c>
+      <c r="I6" s="5">
+        <v>42.8</v>
       </c>
       <c r="J6" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K6" s="1">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="L6" s="1">
-        <v>34.4</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="M6" s="1">
-        <v>4.82</v>
-      </c>
-      <c r="N6" s="13">
-        <v>9.69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
+        <v>5.01</v>
+      </c>
+      <c r="N6" s="11">
+        <v>10.1</v>
+      </c>
+      <c r="S6" s="21"/>
+      <c r="U6"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -887,121 +886,127 @@
         <v>108</v>
       </c>
       <c r="F7" s="3">
-        <v>22</v>
+        <v>23.2</v>
       </c>
       <c r="G7" s="1">
-        <v>7</v>
+        <v>8.42</v>
       </c>
       <c r="H7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>31.8</v>
+        <v>2.14</v>
+      </c>
+      <c r="I7" s="5">
+        <v>33</v>
       </c>
       <c r="J7" s="1">
         <v>30.8</v>
       </c>
       <c r="K7" s="1">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="L7" s="1">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="M7" s="1">
-        <v>4.26</v>
-      </c>
-      <c r="N7" s="13">
-        <v>8.57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="16">
-        <v>51</v>
-      </c>
-      <c r="D8" s="15">
+        <v>4.47</v>
+      </c>
+      <c r="N7" s="11">
+        <v>9</v>
+      </c>
+      <c r="S7" s="21"/>
+      <c r="U7"/>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="20"/>
+      <c r="B8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="13">
+        <v>48</v>
+      </c>
+      <c r="D8" s="12">
         <v>959</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="12">
         <v>2480</v>
       </c>
-      <c r="F8" s="17">
-        <v>1820</v>
-      </c>
-      <c r="G8" s="16">
-        <v>1860</v>
-      </c>
-      <c r="H8" s="16">
-        <v>1578</v>
-      </c>
-      <c r="I8" s="16">
-        <v>2136</v>
-      </c>
-      <c r="J8" s="16">
-        <v>558</v>
-      </c>
-      <c r="K8" s="16">
-        <v>411</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="16">
-        <v>4.8</v>
-      </c>
-      <c r="N8" s="18">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="F8" s="14">
+        <v>1800</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1815</v>
+      </c>
+      <c r="H8" s="13">
+        <v>1549</v>
+      </c>
+      <c r="I8" s="17">
+        <v>2102</v>
+      </c>
+      <c r="J8" s="13">
+        <v>554</v>
+      </c>
+      <c r="K8" s="13">
+        <v>425</v>
+      </c>
+      <c r="L8" s="13">
+        <v>392</v>
+      </c>
+      <c r="M8" s="13">
+        <v>56.6</v>
+      </c>
+      <c r="N8" s="15">
+        <v>114</v>
+      </c>
+      <c r="S8" s="21"/>
+      <c r="U8"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>47</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>1928</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>2131</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>2020</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>1978</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>1946</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="16">
         <v>2110</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>166</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="8">
         <v>63.2</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="8">
         <v>79.599999999999994</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="8">
         <v>11.6</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="10">
         <v>23.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="U9"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="19"/>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1038,14 +1043,16 @@
       <c r="M10" s="1">
         <v>0.114</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="11">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="U10"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="19"/>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1">
         <v>47</v>
@@ -1080,14 +1087,16 @@
       <c r="M11" s="1">
         <v>0.127</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="11">
         <v>0.255</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="U11"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1">
         <v>47</v>
@@ -1122,14 +1131,14 @@
       <c r="M12" s="1">
         <v>0.38300000000000001</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="11">
         <v>0.77</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="19"/>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1">
         <v>47</v>
@@ -1164,14 +1173,14 @@
       <c r="M13" s="1">
         <v>7.77</v>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="11">
         <v>15.6</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="19"/>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1">
         <v>47</v>
@@ -1206,49 +1215,49 @@
       <c r="M14" s="1">
         <v>5.4</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="11">
         <v>10.9</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="16">
+    <row r="15" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="20"/>
+      <c r="B15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="13">
         <v>47</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="12">
         <v>463</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="12">
         <v>1382</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="14">
         <v>955</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="13">
         <v>979</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="13">
         <v>734</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="17">
         <v>1140</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="13">
         <v>405</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="13">
         <v>299</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="13">
         <v>241</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="13">
         <v>35.200000000000003</v>
       </c>
-      <c r="N15" s="18">
+      <c r="N15" s="15">
         <v>70.900000000000006</v>
       </c>
     </row>
